--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Documents/GitHub/Publication_Tracker/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59DEF7B1-1F52-9A43-93A5-6DFE403CE4D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCDE1A78-3FDE-7247-B13D-1FB706601494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="70">
   <si>
     <t>Publication Year</t>
   </si>
@@ -139,9 +139,6 @@
     <t>CVPR</t>
   </si>
   <si>
-    <t>Segmentation</t>
-  </si>
-  <si>
     <t>Planned</t>
   </si>
   <si>
@@ -166,9 +163,6 @@
     <t>ACL</t>
   </si>
   <si>
-    <t>MedLLM</t>
-  </si>
-  <si>
     <t>Dec</t>
   </si>
   <si>
@@ -224,6 +218,33 @@
   </si>
   <si>
     <t>Nature MI/ IEEE</t>
+  </si>
+  <si>
+    <t>IJCAI</t>
+  </si>
+  <si>
+    <t>Jan</t>
+  </si>
+  <si>
+    <t>tbd - MR</t>
+  </si>
+  <si>
+    <t>Segmentation - PK</t>
+  </si>
+  <si>
+    <t>LongMoE - Resubmission</t>
+  </si>
+  <si>
+    <t>CAMOS - Resubmission</t>
+  </si>
+  <si>
+    <t>tbd - MH</t>
+  </si>
+  <si>
+    <t>MedLLM - Resubmission</t>
+  </si>
+  <si>
+    <t>tbd - PK</t>
   </si>
 </sst>
 </file>
@@ -818,63 +839,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -893,6 +857,63 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -946,8 +967,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PublicationsTable" displayName="PublicationsTable" ref="A1:M9" totalsRowShown="0">
-  <autoFilter ref="A1:M9" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PublicationsTable" displayName="PublicationsTable" ref="A1:M10" totalsRowShown="0">
+  <autoFilter ref="A1:M10" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Publication Year"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Venue"/>
@@ -1162,7 +1183,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1408,24 +1429,24 @@
         <v>46339</v>
       </c>
       <c r="E7" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="G7" s="10" t="s">
         <v>35</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>36</v>
       </c>
       <c r="H7" s="10" t="s">
         <v>29</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M7" s="6">
         <v>46292</v>
@@ -1436,89 +1457,311 @@
         <v>2027</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D8" s="11">
-        <v>46376</v>
+        <v>46339</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="F8" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="10" t="s">
         <v>35</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>40</v>
       </c>
       <c r="H8" s="10" t="s">
         <v>29</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="14" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="M8" s="6">
         <v>46292</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="34" customHeight="1">
-      <c r="A9" s="9">
+      <c r="A9" s="8">
         <v>2027</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="11">
+        <v>46376</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K9" s="4"/>
+      <c r="L9" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="M9" s="6">
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="34" customHeight="1">
+      <c r="A10" s="9">
+        <v>2027</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="13">
+        <v>46398</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="H10" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K10" s="5"/>
+      <c r="L10" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="M10" s="7">
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="34" customHeight="1">
+      <c r="A11" s="9">
+        <v>2027</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D11" s="13">
+        <v>46398</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K11" s="5"/>
+      <c r="L11" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="M11" s="7">
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="34" customHeight="1">
+      <c r="A12" s="9">
+        <v>2027</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="13">
         <v>46415</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E12" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="H12" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="12" t="s">
+      <c r="I12" s="5"/>
+      <c r="J12" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K12" s="5"/>
+      <c r="L12" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="H9" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="K9" s="5"/>
-      <c r="L9" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="M9" s="7">
+      <c r="M12" s="7">
         <v>46292</v>
       </c>
     </row>
+    <row r="13" spans="1:13" ht="34" customHeight="1">
+      <c r="A13" s="9">
+        <v>2027</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="13">
+        <v>46415</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K13" s="5"/>
+      <c r="L13" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="M13" s="7">
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="34" customHeight="1">
+      <c r="A14" s="9">
+        <v>2027</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="13">
+        <v>46415</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K14" s="5"/>
+      <c r="L14" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="M14" s="7">
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="34" customHeight="1">
+      <c r="A15" s="9">
+        <v>2027</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="13">
+        <v>46415</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K15" s="5"/>
+      <c r="L15" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="M15" s="7">
+        <v>46292</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="F2:F200">
+  <conditionalFormatting sqref="F2:F202">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Accepted"/>
     <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Submitted"/>
     <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="Planned"/>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" sqref="F2:F200" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="F2:F202" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Accepted,Submitted,In Review,Revision,Planned,On Hold,Withdrawn,Rejected"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="H2:H200" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" sqref="H2:H202" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"High,Medium,Low,Archive"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="C2:C200" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" sqref="C2:C202" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Conference,Workshop,Journal"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1540,75 +1783,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="31" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+    </row>
+    <row r="2" spans="1:6" ht="31" customHeight="1">
+      <c r="A2" s="37"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+    </row>
+    <row r="4" spans="1:6" ht="15">
+      <c r="A4" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="39"/>
+      <c r="C4" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-    </row>
-    <row r="2" spans="1:6" ht="31" customHeight="1">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-    </row>
-    <row r="4" spans="1:6" ht="15">
-      <c r="A4" s="31" t="s">
+      <c r="D4" s="41"/>
+      <c r="E4" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="32"/>
-      <c r="C4" s="33" t="s">
+      <c r="F4" s="43"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="44">
+        <f>COUNTIF(Publications!$F$2:$F$103,"Accepted")</f>
+        <v>3</v>
+      </c>
+      <c r="B5" s="45"/>
+      <c r="C5" s="48">
+        <f>COUNTIF(Publications!$F$2:$F$103,"Submitted")</f>
+        <v>2</v>
+      </c>
+      <c r="D5" s="49"/>
+      <c r="E5" s="52">
+        <f>COUNTIF(Publications!$F$2:$F$103,"Planned")</f>
+        <v>9</v>
+      </c>
+      <c r="F5" s="53"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="46"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="55"/>
+    </row>
+    <row r="8" spans="1:6" ht="16">
+      <c r="A8" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="F4" s="36"/>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="37">
-        <f>COUNTIF(Publications!$F$2:$F$101,"Accepted")</f>
-        <v>3</v>
-      </c>
-      <c r="B5" s="38"/>
-      <c r="C5" s="41">
-        <f>COUNTIF(Publications!$F$2:$F$101,"Submitted")</f>
-        <v>2</v>
-      </c>
-      <c r="D5" s="42"/>
-      <c r="E5" s="45">
-        <f>COUNTIF(Publications!$F$2:$F$101,"Planned")</f>
-        <v>3</v>
-      </c>
-      <c r="F5" s="46"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="39"/>
-      <c r="B6" s="40"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="48"/>
-    </row>
-    <row r="8" spans="1:6" ht="16">
-      <c r="A8" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" s="49"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
     </row>
     <row r="9" spans="1:6" ht="15">
       <c r="A9" s="16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>1</v>
@@ -1617,13 +1860,13 @@
         <v>3</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E9" s="17" t="s">
         <v>5</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="26" customHeight="1">
@@ -1680,99 +1923,99 @@
     </row>
     <row r="12" spans="1:6" ht="26" customHeight="1">
       <c r="A12" s="19">
-        <f>Publications!A7</f>
+        <f>Publications!A8</f>
         <v>2027</v>
       </c>
       <c r="B12" s="20" t="str">
-        <f>Publications!B7</f>
+        <f>Publications!B8</f>
         <v>CVPR</v>
       </c>
       <c r="C12" s="21">
-        <f>Publications!D7</f>
+        <f>Publications!D8</f>
         <v>46339</v>
       </c>
       <c r="D12" s="20" t="str">
-        <f>Publications!E7</f>
-        <v>Segmentation</v>
+        <f>Publications!E8</f>
+        <v>tbd - MR</v>
       </c>
       <c r="E12" s="20" t="str">
-        <f>Publications!F7</f>
+        <f>Publications!F8</f>
         <v>Planned</v>
       </c>
       <c r="F12" s="22" t="str">
-        <f>Publications!G7</f>
+        <f>Publications!G8</f>
         <v>Oct</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="26" customHeight="1">
       <c r="A13" s="19">
-        <f>Publications!A8</f>
+        <f>Publications!A9</f>
         <v>2027</v>
       </c>
       <c r="B13" s="20" t="str">
-        <f>Publications!B8</f>
+        <f>Publications!B9</f>
         <v>Nature MI/ IEEE</v>
       </c>
       <c r="C13" s="21">
-        <f>Publications!D8</f>
+        <f>Publications!D9</f>
         <v>46376</v>
       </c>
       <c r="D13" s="20" t="str">
-        <f>Publications!E8</f>
+        <f>Publications!E9</f>
         <v>INCLAIR</v>
       </c>
       <c r="E13" s="20" t="str">
-        <f>Publications!F8</f>
+        <f>Publications!F9</f>
         <v>Planned</v>
       </c>
       <c r="F13" s="22" t="str">
-        <f>Publications!G8</f>
+        <f>Publications!G9</f>
         <v>Nov</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="26" customHeight="1">
       <c r="A14" s="23">
-        <f>Publications!A9</f>
+        <f>Publications!A10</f>
         <v>2027</v>
       </c>
       <c r="B14" s="24" t="str">
-        <f>Publications!B9</f>
-        <v>ACL</v>
+        <f>Publications!B10</f>
+        <v>IJCAI</v>
       </c>
       <c r="C14" s="25">
-        <f>Publications!D9</f>
-        <v>46415</v>
+        <f>Publications!D10</f>
+        <v>46398</v>
       </c>
       <c r="D14" s="24" t="str">
-        <f>Publications!E9</f>
-        <v>MedLLM</v>
+        <f>Publications!E10</f>
+        <v>MedLLM - Resubmission</v>
       </c>
       <c r="E14" s="24" t="str">
-        <f>Publications!F9</f>
+        <f>Publications!F10</f>
         <v>Planned</v>
       </c>
       <c r="F14" s="26" t="str">
-        <f>Publications!G9</f>
+        <f>Publications!G10</f>
         <v>Dec</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="50" t="s">
-        <v>55</v>
-      </c>
-      <c r="B16" s="51"/>
-      <c r="C16" s="51"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="52"/>
+      <c r="A16" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="33"/>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="53"/>
-      <c r="B17" s="54"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="55"/>
+      <c r="A17" s="34"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -1825,7 +2068,7 @@
         <v>28</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C3" s="28" t="s">
         <v>14</v>
@@ -1833,10 +2076,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="28" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C4" s="28" t="s">
         <v>21</v>
@@ -1844,7 +2087,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="28" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B5" s="28" t="s">
         <v>17</v>
@@ -1853,28 +2096,28 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B6" s="28"/>
       <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="28" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B7" s="28"/>
       <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="28" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B8" s="28"/>
       <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="29" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B9" s="29"/>
       <c r="C9" s="29"/>
